--- a/human_resources_forms/001_leaders_nomination_form--human_resources_forms.xlsx
+++ b/human_resources_forms/001_leaders_nomination_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_1</t>
+          <t>leader_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Leaders Nomination Form</t>
+          <t>Leader's Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +543,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_2</t>
+          <t>leadership_position</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nomination Information</t>
+          <t>Leadership Position</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_3</t>
+          <t>leader_expertise</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Leadership Position</t>
+          <t>Leader's Expertise</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_4</t>
+          <t>nomination_justification</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Leadership Expertise</t>
+          <t>Nomination Justification</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +612,18 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_5</t>
+          <t>leader_contact</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nomination Justification</t>
+          <t>Leader's Contact Info</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,64 +635,64 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_6</t>
+          <t>nomination_reasons</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nominee Bio</t>
+          <t>Nomination Reasons</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_7</t>
+          <t>submission_date</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nominee Contact</t>
+          <t>Form Submission Date</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_8</t>
+          <t>form_submission_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nomination Justification</t>
+          <t>Form Submission Time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_9</t>
+          <t>leader_strengths</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nominee Leadership Position</t>
+          <t>Leader's Strengths</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_10</t>
+          <t>leader_areas_of_improvement</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nominee Expertise</t>
+          <t>Leader's Areas of Improvement</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,18 +750,18 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_11</t>
+          <t>nomination_review</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nomination Status</t>
+          <t>Nomination Review</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_12</t>
+          <t>form_submission</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -784,116 +784,116 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_submission_page_13</t>
+          <t>nomination_type</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nomination Status</t>
+          <t>Nomination Type</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>form_submission_page_14</t>
+          <t>nomination_status</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nomination Type</t>
+          <t>Nomination Status</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>form_submission_page_15</t>
+          <t>leader_bio</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Form Submission Date</t>
+          <t>Leader's Bio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_submission_page_16</t>
+          <t>leader_nomination_form</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Form Submission Time</t>
+          <t>Leader's Nomination Form</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>form_submission_page_17</t>
+          <t>leader_leadership_position</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nomination Status</t>
+          <t>Leader's Leadership Position</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,17 +906,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>form_submission_page_18</t>
+          <t>leader_expertise_area</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nomination Type</t>
+          <t>Leader's Expertise Area</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,18 +934,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>form_submission_page_19</t>
+          <t>submission_review</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Form Submission</t>
+          <t>Form Submission Review</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -957,58 +957,58 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>form_submission_page_20</t>
+          <t>submission_type</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Form Submission</t>
+          <t>Form Submission Type</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>form_submission_page_21</t>
+          <t>leader_contact_info</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Leaders Nomination Form</t>
+          <t>Leader Contact Info</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>leaders_nomination_form</t>
+          <t>form_submission_page_1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Leaders Nomination Form</t>
+          <t>Form Submission Page 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,17 +1021,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>leaders_nomination_form</t>
+          <t>leader_organizational_position</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Leaders Nomination Form</t>
+          <t>Leader's Organizational Position</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>form_submission_page_24</t>
+          <t>form_submission_page_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Nomination Status</t>
+          <t>Form Submission Page 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,23 +1067,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>form_submission_page_25</t>
+          <t>leaders_nominated</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nomination Type</t>
+          <t>Leaders Nominated</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,884 +1126,442 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_11_choices</t>
+          <t>nomination_review_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_11_choices</t>
+          <t>nomination_review_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_11_choices</t>
+          <t>nomination_review_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_11_choices</t>
+          <t>form_submission_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>submitted</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Submitted</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_12_choices</t>
+          <t>form_submission_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_12_choices</t>
+          <t>form_submission_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_12_choices</t>
+          <t>nomination_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>type_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>leaders_nomination_form_page_12_choices</t>
+          <t>nomination_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Type 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_submission_page_13_choices</t>
+          <t>nomination_type_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>type_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Type 3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_submission_page_13_choices</t>
+          <t>nomination_type_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>type_4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Type 4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>form_submission_page_13_choices</t>
+          <t>nomination_status_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>form_submission_page_13_choices</t>
+          <t>nomination_status_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>form_submission_page_14_choices</t>
+          <t>nomination_status_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>form_submission_page_14_choices</t>
+          <t>leader_nomination_form_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>form_submission_page_14_choices</t>
+          <t>leader_nomination_form_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>form_submission_page_14_choices</t>
+          <t>leader_nomination_form_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>form_submission_page_17_choices</t>
+          <t>submission_review_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>reviewed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Reviewed</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>form_submission_page_17_choices</t>
+          <t>submission_review_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>unreviewed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Unreviewed</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>form_submission_page_17_choices</t>
+          <t>submission_review_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>form_submission_page_17_choices</t>
+          <t>submission_type_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>type_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>form_submission_page_18_choices</t>
+          <t>submission_type_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Type 2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>form_submission_page_18_choices</t>
+          <t>submission_type_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>type_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Type 3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>form_submission_page_18_choices</t>
+          <t>submission_type_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>type_4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Type 4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>form_submission_page_18_choices</t>
+          <t>form_submission_page_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>form_submission_page_19_choices</t>
+          <t>form_submission_page_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>form_submission_page_19_choices</t>
+          <t>form_submission_page_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>form_submission_page_19_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>form_submission_page_19_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>form_submission_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>form_submission_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>form_submission_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>form_submission_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>form_submission_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>form_submission_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>form_submission_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>form_submission_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>leaders_nomination_form_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>leaders_nomination_form_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>leaders_nomination_form_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>leaders_nomination_form_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>leaders_nomination_form_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>leaders_nomination_form_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>leaders_nomination_form_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>leaders_nomination_form_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>form_submission_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>form_submission_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>form_submission_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>form_submission_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>form_submission_page_25_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>form_submission_page_25_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>form_submission_page_25_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>form_submission_page_25_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Option 4</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
